--- a/astro-site/public/dl/pack-appcc/06-registro-trazabilidad.xlsx
+++ b/astro-site/public/dl/pack-appcc/06-registro-trazabilidad.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Trazabilidad" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trazabilidad" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt formatCode="DD/MM/YYYY" numFmtId="164"/>
+    <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -117,33 +117,33 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="11">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="7" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -503,15 +503,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -519,6 +520,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -526,9 +528,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" t="inlineStr"/>
-    </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -557,13 +557,19 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" t="inlineStr"/>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>— Pack de Plantillas APPCC · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/pack-appcc · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -571,7 +577,16 @@
   <mergeCells count="1">
     <mergeCell ref="B2"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -580,20 +595,20 @@
   <sheetPr>
     <tabColor rgb="009C27B0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="14"/>
-    <col customWidth="1" max="2" min="2" width="25"/>
-    <col customWidth="1" max="3" min="3" width="15"/>
-    <col customWidth="1" max="4" min="4" width="20"/>
-    <col customWidth="1" max="5" min="5" width="14"/>
-    <col customWidth="1" max="6" min="6" width="14"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
-    <col customWidth="1" max="8" min="8" width="15"/>
-    <col customWidth="1" max="9" min="9" width="20"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -610,6 +625,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1042,6 +1058,7 @@
       <c r="H39" s="8" t="n"/>
       <c r="I39" s="8" t="n"/>
     </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
@@ -1067,7 +1084,15 @@
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup orientation="landscape"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/pack-appcc/06-registro-trazabilidad.xlsx
+++ b/astro-site/public/dl/pack-appcc/06-registro-trazabilidad.xlsx
@@ -9,8 +9,15 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trazabilidad" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Salida y uso interno" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$B$23</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Trazabilidad'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Trazabilidad'!$A$1:$I$49</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Salida y uso interno'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Salida y uso interno'!$A$1:$G$48</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -20,7 +27,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -72,8 +79,31 @@
       <color rgb="00999999"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -92,8 +122,18 @@
         <bgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002D2D2D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -115,11 +155,25 @@
         <color rgb="00E0E0E0"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D0D0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -139,6 +193,40 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -505,16 +593,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="95" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1"/>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>Registro de Trazabilidad</t>
         </is>
@@ -522,7 +610,7 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>Cómo usar esta plantilla</t>
         </is>
@@ -530,54 +618,97 @@
     </row>
     <row r="5"/>
     <row r="6">
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>▸ Registra TODOS los productos que entran y salen</t>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>▸ Hoja «Trazabilidad»: TODO lo que ENTRA, con su lote y su proveedor. Es la trazabilidad hacia atrás.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>▸ Anota siempre: lote, proveedor, fecha entrada, fecha caducidad</t>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>▸ Hoja «Salida y uso interno»: en qué elaboración y a qué servicio fue cada lote. Es la trazabilidad hacia adelante, y es la que responde a «¿a quién se sirvió esto?» en una alerta.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>▸ En caso de alerta alimentaria, debes poder rastrear el origen en &lt; 4 horas</t>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>▸ Anota siempre lote, proveedor, fecha de entrada y fecha de caducidad. El mismo nº de lote debe aparecer en el registro 05 (recepción) para que las dos hojas se enganchen.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>▸ Obligatorio según Reglamento (CE) 178/2002</t>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>▸ Obligatorio según el Reglamento (CE) 178/2002, arts. 18 y 19.</t>
         </is>
       </c>
     </row>
     <row r="10"/>
     <row r="11">
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>— Pack de Plantillas APPCC · AI Chef Pro · aichef.pro</t>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Qué exige realmente el Reg. (CE) 178/2002</t>
         </is>
       </c>
     </row>
     <row r="12"/>
     <row r="13">
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/pack-appcc · info@aichef.pro</t>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>▸ Art. 18: poder identificar a quién se compró y a quién se suministró cada producto, y entregar esa información de forma inmediata a requerimiento de la autoridad competente. NO fija un plazo de «4 horas»: eso es de estándares privados IFS/BRC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>▸ Art. 19: si sospechas que un alimento que has puesto en el mercado puede ser nocivo, retirarlo e informar de inmediato a la autoridad sanitaria de tu comunidad autónoma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>Frecuencia y archivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>▸ Frecuencia: una línea por entrada y una línea por salida. 40 filas por hoja (aprox. un mes).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>▸ Conservar al menos 2 años (trazabilidad y proveedores: 5); el Reg. (CE) 178/2002 exige trazabilidad pero no fija plazo — consulta la guía de prácticas correctas de higiene de tu comunidad autónoma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>— Pack de Plantillas APPCC · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/pack-appcc · info@aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2"/>
-  </mergeCells>
-  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageMargins left="0.55" right="0.55" top="0.55" bottom="0.55" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
@@ -597,494 +728,1198 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Registro de Trazabilidad — Entrada de Productos</t>
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>Registro de Trazabilidad — Entrada de productos (trazabilidad hacia atrás)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Mes: _______________</t>
+          <t>Mes: _______________    La trazabilidad hacia adelante va en la hoja «Salida y uso interno».</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Fecha Entrada</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>Fecha entrada</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>Producto</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Nº Lote</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Nº lote</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>Proveedor</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Fecha Caducidad</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Fecha Consumo</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>Fecha caducidad</t>
+        </is>
+      </c>
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <t>Fecha consumo</t>
+        </is>
+      </c>
+      <c r="G4" s="15" t="inlineStr">
         <is>
           <t>Cantidad</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>Destino / Uso</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="H4" s="15" t="inlineStr">
+        <is>
+          <t>Destino / uso</t>
+        </is>
+      </c>
+      <c r="I4" s="15" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="7" t="n"/>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="9" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="7" t="n"/>
-      <c r="G5" s="9" t="n"/>
-      <c r="H5" s="8" t="n"/>
-      <c r="I5" s="8" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="n"/>
-      <c r="B6" s="8" t="n"/>
-      <c r="C6" s="9" t="n"/>
-      <c r="D6" s="8" t="n"/>
-      <c r="E6" s="7" t="n"/>
-      <c r="F6" s="7" t="n"/>
-      <c r="G6" s="9" t="n"/>
-      <c r="H6" s="8" t="n"/>
-      <c r="I6" s="8" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="n"/>
-      <c r="B7" s="8" t="n"/>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="8" t="n"/>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7" t="n"/>
-      <c r="G7" s="9" t="n"/>
-      <c r="H7" s="8" t="n"/>
-      <c r="I7" s="8" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="n"/>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="9" t="n"/>
-      <c r="D8" s="8" t="n"/>
-      <c r="E8" s="7" t="n"/>
-      <c r="F8" s="7" t="n"/>
-      <c r="G8" s="9" t="n"/>
-      <c r="H8" s="8" t="n"/>
-      <c r="I8" s="8" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="8" t="n"/>
-      <c r="C9" s="9" t="n"/>
-      <c r="D9" s="8" t="n"/>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="n"/>
-      <c r="G9" s="9" t="n"/>
-      <c r="H9" s="8" t="n"/>
-      <c r="I9" s="8" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="n"/>
-      <c r="B10" s="8" t="n"/>
-      <c r="C10" s="9" t="n"/>
-      <c r="D10" s="8" t="n"/>
-      <c r="E10" s="7" t="n"/>
-      <c r="F10" s="7" t="n"/>
-      <c r="G10" s="9" t="n"/>
-      <c r="H10" s="8" t="n"/>
-      <c r="I10" s="8" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="8" t="n"/>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="8" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7" t="n"/>
-      <c r="G11" s="9" t="n"/>
-      <c r="H11" s="8" t="n"/>
-      <c r="I11" s="8" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="n"/>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="9" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n"/>
-      <c r="G12" s="9" t="n"/>
-      <c r="H12" s="8" t="n"/>
-      <c r="I12" s="8" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="n"/>
-      <c r="B13" s="8" t="n"/>
-      <c r="C13" s="9" t="n"/>
-      <c r="D13" s="8" t="n"/>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="9" t="n"/>
-      <c r="H13" s="8" t="n"/>
-      <c r="I13" s="8" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="n"/>
-      <c r="B14" s="8" t="n"/>
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="8" t="n"/>
-      <c r="E14" s="7" t="n"/>
-      <c r="F14" s="7" t="n"/>
-      <c r="G14" s="9" t="n"/>
-      <c r="H14" s="8" t="n"/>
-      <c r="I14" s="8" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="n"/>
-      <c r="B15" s="8" t="n"/>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="8" t="n"/>
-      <c r="E15" s="7" t="n"/>
-      <c r="F15" s="7" t="n"/>
-      <c r="G15" s="9" t="n"/>
-      <c r="H15" s="8" t="n"/>
-      <c r="I15" s="8" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="n"/>
-      <c r="B16" s="8" t="n"/>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="8" t="n"/>
-      <c r="E16" s="7" t="n"/>
-      <c r="F16" s="7" t="n"/>
-      <c r="G16" s="9" t="n"/>
-      <c r="H16" s="8" t="n"/>
-      <c r="I16" s="8" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="n"/>
-      <c r="B17" s="8" t="n"/>
-      <c r="C17" s="9" t="n"/>
-      <c r="D17" s="8" t="n"/>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="7" t="n"/>
-      <c r="G17" s="9" t="n"/>
-      <c r="H17" s="8" t="n"/>
-      <c r="I17" s="8" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="n"/>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="9" t="n"/>
-      <c r="D18" s="8" t="n"/>
-      <c r="E18" s="7" t="n"/>
-      <c r="F18" s="7" t="n"/>
-      <c r="G18" s="9" t="n"/>
-      <c r="H18" s="8" t="n"/>
-      <c r="I18" s="8" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="n"/>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" s="9" t="n"/>
-      <c r="D19" s="8" t="n"/>
-      <c r="E19" s="7" t="n"/>
-      <c r="F19" s="7" t="n"/>
-      <c r="G19" s="9" t="n"/>
-      <c r="H19" s="8" t="n"/>
-      <c r="I19" s="8" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="n"/>
-      <c r="B20" s="8" t="n"/>
-      <c r="C20" s="9" t="n"/>
-      <c r="D20" s="8" t="n"/>
-      <c r="E20" s="7" t="n"/>
-      <c r="F20" s="7" t="n"/>
-      <c r="G20" s="9" t="n"/>
-      <c r="H20" s="8" t="n"/>
-      <c r="I20" s="8" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="n"/>
-      <c r="B21" s="8" t="n"/>
-      <c r="C21" s="9" t="n"/>
-      <c r="D21" s="8" t="n"/>
-      <c r="E21" s="7" t="n"/>
-      <c r="F21" s="7" t="n"/>
-      <c r="G21" s="9" t="n"/>
-      <c r="H21" s="8" t="n"/>
-      <c r="I21" s="8" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="n"/>
-      <c r="B22" s="8" t="n"/>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="8" t="n"/>
-      <c r="E22" s="7" t="n"/>
-      <c r="F22" s="7" t="n"/>
-      <c r="G22" s="9" t="n"/>
-      <c r="H22" s="8" t="n"/>
-      <c r="I22" s="8" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="n"/>
-      <c r="B23" s="8" t="n"/>
-      <c r="C23" s="9" t="n"/>
-      <c r="D23" s="8" t="n"/>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="n"/>
-      <c r="G23" s="9" t="n"/>
-      <c r="H23" s="8" t="n"/>
-      <c r="I23" s="8" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="n"/>
-      <c r="B24" s="8" t="n"/>
-      <c r="C24" s="9" t="n"/>
-      <c r="D24" s="8" t="n"/>
-      <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="n"/>
-      <c r="G24" s="9" t="n"/>
-      <c r="H24" s="8" t="n"/>
-      <c r="I24" s="8" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="n"/>
-      <c r="B25" s="8" t="n"/>
-      <c r="C25" s="9" t="n"/>
-      <c r="D25" s="8" t="n"/>
-      <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="n"/>
-      <c r="G25" s="9" t="n"/>
-      <c r="H25" s="8" t="n"/>
-      <c r="I25" s="8" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="n"/>
-      <c r="B26" s="8" t="n"/>
-      <c r="C26" s="9" t="n"/>
-      <c r="D26" s="8" t="n"/>
-      <c r="E26" s="7" t="n"/>
-      <c r="F26" s="7" t="n"/>
-      <c r="G26" s="9" t="n"/>
-      <c r="H26" s="8" t="n"/>
-      <c r="I26" s="8" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="n"/>
-      <c r="B27" s="8" t="n"/>
-      <c r="C27" s="9" t="n"/>
-      <c r="D27" s="8" t="n"/>
-      <c r="E27" s="7" t="n"/>
-      <c r="F27" s="7" t="n"/>
-      <c r="G27" s="9" t="n"/>
-      <c r="H27" s="8" t="n"/>
-      <c r="I27" s="8" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="n"/>
-      <c r="B28" s="8" t="n"/>
-      <c r="C28" s="9" t="n"/>
-      <c r="D28" s="8" t="n"/>
-      <c r="E28" s="7" t="n"/>
-      <c r="F28" s="7" t="n"/>
-      <c r="G28" s="9" t="n"/>
-      <c r="H28" s="8" t="n"/>
-      <c r="I28" s="8" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="n"/>
-      <c r="B29" s="8" t="n"/>
-      <c r="C29" s="9" t="n"/>
-      <c r="D29" s="8" t="n"/>
-      <c r="E29" s="7" t="n"/>
-      <c r="F29" s="7" t="n"/>
-      <c r="G29" s="9" t="n"/>
-      <c r="H29" s="8" t="n"/>
-      <c r="I29" s="8" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="n"/>
-      <c r="B30" s="8" t="n"/>
-      <c r="C30" s="9" t="n"/>
-      <c r="D30" s="8" t="n"/>
-      <c r="E30" s="7" t="n"/>
-      <c r="F30" s="7" t="n"/>
-      <c r="G30" s="9" t="n"/>
-      <c r="H30" s="8" t="n"/>
-      <c r="I30" s="8" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="n"/>
-      <c r="B31" s="8" t="n"/>
-      <c r="C31" s="9" t="n"/>
-      <c r="D31" s="8" t="n"/>
-      <c r="E31" s="7" t="n"/>
-      <c r="F31" s="7" t="n"/>
-      <c r="G31" s="9" t="n"/>
-      <c r="H31" s="8" t="n"/>
-      <c r="I31" s="8" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="n"/>
-      <c r="B32" s="8" t="n"/>
-      <c r="C32" s="9" t="n"/>
-      <c r="D32" s="8" t="n"/>
-      <c r="E32" s="7" t="n"/>
-      <c r="F32" s="7" t="n"/>
-      <c r="G32" s="9" t="n"/>
-      <c r="H32" s="8" t="n"/>
-      <c r="I32" s="8" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="n"/>
-      <c r="B33" s="8" t="n"/>
-      <c r="C33" s="9" t="n"/>
-      <c r="D33" s="8" t="n"/>
-      <c r="E33" s="7" t="n"/>
-      <c r="F33" s="7" t="n"/>
-      <c r="G33" s="9" t="n"/>
-      <c r="H33" s="8" t="n"/>
-      <c r="I33" s="8" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="n"/>
-      <c r="B34" s="8" t="n"/>
-      <c r="C34" s="9" t="n"/>
-      <c r="D34" s="8" t="n"/>
-      <c r="E34" s="7" t="n"/>
-      <c r="F34" s="7" t="n"/>
-      <c r="G34" s="9" t="n"/>
-      <c r="H34" s="8" t="n"/>
-      <c r="I34" s="8" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="n"/>
-      <c r="B35" s="8" t="n"/>
-      <c r="C35" s="9" t="n"/>
-      <c r="D35" s="8" t="n"/>
-      <c r="E35" s="7" t="n"/>
-      <c r="F35" s="7" t="n"/>
-      <c r="G35" s="9" t="n"/>
-      <c r="H35" s="8" t="n"/>
-      <c r="I35" s="8" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="n"/>
-      <c r="B36" s="8" t="n"/>
-      <c r="C36" s="9" t="n"/>
-      <c r="D36" s="8" t="n"/>
-      <c r="E36" s="7" t="n"/>
-      <c r="F36" s="7" t="n"/>
-      <c r="G36" s="9" t="n"/>
-      <c r="H36" s="8" t="n"/>
-      <c r="I36" s="8" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="n"/>
-      <c r="B37" s="8" t="n"/>
-      <c r="C37" s="9" t="n"/>
-      <c r="D37" s="8" t="n"/>
-      <c r="E37" s="7" t="n"/>
-      <c r="F37" s="7" t="n"/>
-      <c r="G37" s="9" t="n"/>
-      <c r="H37" s="8" t="n"/>
-      <c r="I37" s="8" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="n"/>
-      <c r="B38" s="8" t="n"/>
-      <c r="C38" s="9" t="n"/>
-      <c r="D38" s="8" t="n"/>
-      <c r="E38" s="7" t="n"/>
-      <c r="F38" s="7" t="n"/>
-      <c r="G38" s="9" t="n"/>
-      <c r="H38" s="8" t="n"/>
-      <c r="I38" s="8" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="n"/>
-      <c r="B39" s="8" t="n"/>
-      <c r="C39" s="9" t="n"/>
-      <c r="D39" s="8" t="n"/>
-      <c r="E39" s="7" t="n"/>
-      <c r="F39" s="7" t="n"/>
-      <c r="G39" s="9" t="n"/>
-      <c r="H39" s="8" t="n"/>
-      <c r="I39" s="8" t="n"/>
-    </row>
-    <row r="40"/>
-    <row r="41">
-      <c r="A41" s="10" t="inlineStr">
-        <is>
-          <t>En caso de alerta alimentaria: localizar lote afectado, retirar producto, notificar a autoridad sanitaria.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="10" t="inlineStr">
-        <is>
-          <t>Conservar registros mínimo 5 años (Reglamento CE 178/2002).</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="10" t="inlineStr">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>05/09/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>Merluza fresca</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>L-2026-0912</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>Pescados de la Ría S.L.</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>06/09/2026</t>
+        </is>
+      </c>
+      <c r="G5" s="18" t="inlineStr">
+        <is>
+          <t>8,4 kg</t>
+        </is>
+      </c>
+      <c r="H5" s="17" t="inlineStr">
+        <is>
+          <t>Servicio de mediodía</t>
+        </is>
+      </c>
+      <c r="I5" s="17" t="inlineStr">
+        <is>
+          <t>(ejemplo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>05/09/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>Canal de ternera</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>L-2026-0913</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>Cárnicas del Norte</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="G6" s="18" t="inlineStr">
+        <is>
+          <t>22 kg</t>
+        </is>
+      </c>
+      <c r="H6" s="17" t="inlineStr">
+        <is>
+          <t>Despiece y congelación</t>
+        </is>
+      </c>
+      <c r="I6" s="17" t="inlineStr">
+        <is>
+          <t>(ejemplo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>05/09/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>Nata 35 % MG</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>L-2026-0915</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>Lácteos Vega</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="G7" s="18" t="inlineStr">
+        <is>
+          <t>6 L</t>
+        </is>
+      </c>
+      <c r="H7" s="17" t="inlineStr">
+        <is>
+          <t>Obrador — postres</t>
+        </is>
+      </c>
+      <c r="I7" s="17" t="inlineStr">
+        <is>
+          <t>(ejemplo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="16" t="n"/>
+      <c r="B8" s="17" t="n"/>
+      <c r="C8" s="18" t="n"/>
+      <c r="D8" s="17" t="n"/>
+      <c r="E8" s="16" t="n"/>
+      <c r="F8" s="16" t="n"/>
+      <c r="G8" s="18" t="n"/>
+      <c r="H8" s="17" t="n"/>
+      <c r="I8" s="17" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="16" t="n"/>
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="18" t="n"/>
+      <c r="D9" s="17" t="n"/>
+      <c r="E9" s="16" t="n"/>
+      <c r="F9" s="16" t="n"/>
+      <c r="G9" s="18" t="n"/>
+      <c r="H9" s="17" t="n"/>
+      <c r="I9" s="17" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="16" t="n"/>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="18" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="16" t="n"/>
+      <c r="F10" s="16" t="n"/>
+      <c r="G10" s="18" t="n"/>
+      <c r="H10" s="17" t="n"/>
+      <c r="I10" s="17" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="16" t="n"/>
+      <c r="B11" s="17" t="n"/>
+      <c r="C11" s="18" t="n"/>
+      <c r="D11" s="17" t="n"/>
+      <c r="E11" s="16" t="n"/>
+      <c r="F11" s="16" t="n"/>
+      <c r="G11" s="18" t="n"/>
+      <c r="H11" s="17" t="n"/>
+      <c r="I11" s="17" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="16" t="n"/>
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="18" t="n"/>
+      <c r="D12" s="17" t="n"/>
+      <c r="E12" s="16" t="n"/>
+      <c r="F12" s="16" t="n"/>
+      <c r="G12" s="18" t="n"/>
+      <c r="H12" s="17" t="n"/>
+      <c r="I12" s="17" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="16" t="n"/>
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="18" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="16" t="n"/>
+      <c r="F13" s="16" t="n"/>
+      <c r="G13" s="18" t="n"/>
+      <c r="H13" s="17" t="n"/>
+      <c r="I13" s="17" t="n"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="16" t="n"/>
+      <c r="B14" s="17" t="n"/>
+      <c r="C14" s="18" t="n"/>
+      <c r="D14" s="17" t="n"/>
+      <c r="E14" s="16" t="n"/>
+      <c r="F14" s="16" t="n"/>
+      <c r="G14" s="18" t="n"/>
+      <c r="H14" s="17" t="n"/>
+      <c r="I14" s="17" t="n"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="16" t="n"/>
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="18" t="n"/>
+      <c r="D15" s="17" t="n"/>
+      <c r="E15" s="16" t="n"/>
+      <c r="F15" s="16" t="n"/>
+      <c r="G15" s="18" t="n"/>
+      <c r="H15" s="17" t="n"/>
+      <c r="I15" s="17" t="n"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="16" t="n"/>
+      <c r="B16" s="17" t="n"/>
+      <c r="C16" s="18" t="n"/>
+      <c r="D16" s="17" t="n"/>
+      <c r="E16" s="16" t="n"/>
+      <c r="F16" s="16" t="n"/>
+      <c r="G16" s="18" t="n"/>
+      <c r="H16" s="17" t="n"/>
+      <c r="I16" s="17" t="n"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="16" t="n"/>
+      <c r="B17" s="17" t="n"/>
+      <c r="C17" s="18" t="n"/>
+      <c r="D17" s="17" t="n"/>
+      <c r="E17" s="16" t="n"/>
+      <c r="F17" s="16" t="n"/>
+      <c r="G17" s="18" t="n"/>
+      <c r="H17" s="17" t="n"/>
+      <c r="I17" s="17" t="n"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="16" t="n"/>
+      <c r="B18" s="17" t="n"/>
+      <c r="C18" s="18" t="n"/>
+      <c r="D18" s="17" t="n"/>
+      <c r="E18" s="16" t="n"/>
+      <c r="F18" s="16" t="n"/>
+      <c r="G18" s="18" t="n"/>
+      <c r="H18" s="17" t="n"/>
+      <c r="I18" s="17" t="n"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="16" t="n"/>
+      <c r="B19" s="17" t="n"/>
+      <c r="C19" s="18" t="n"/>
+      <c r="D19" s="17" t="n"/>
+      <c r="E19" s="16" t="n"/>
+      <c r="F19" s="16" t="n"/>
+      <c r="G19" s="18" t="n"/>
+      <c r="H19" s="17" t="n"/>
+      <c r="I19" s="17" t="n"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="16" t="n"/>
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="18" t="n"/>
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="16" t="n"/>
+      <c r="F20" s="16" t="n"/>
+      <c r="G20" s="18" t="n"/>
+      <c r="H20" s="17" t="n"/>
+      <c r="I20" s="17" t="n"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="16" t="n"/>
+      <c r="B21" s="17" t="n"/>
+      <c r="C21" s="18" t="n"/>
+      <c r="D21" s="17" t="n"/>
+      <c r="E21" s="16" t="n"/>
+      <c r="F21" s="16" t="n"/>
+      <c r="G21" s="18" t="n"/>
+      <c r="H21" s="17" t="n"/>
+      <c r="I21" s="17" t="n"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="16" t="n"/>
+      <c r="B22" s="17" t="n"/>
+      <c r="C22" s="18" t="n"/>
+      <c r="D22" s="17" t="n"/>
+      <c r="E22" s="16" t="n"/>
+      <c r="F22" s="16" t="n"/>
+      <c r="G22" s="18" t="n"/>
+      <c r="H22" s="17" t="n"/>
+      <c r="I22" s="17" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="16" t="n"/>
+      <c r="B23" s="17" t="n"/>
+      <c r="C23" s="18" t="n"/>
+      <c r="D23" s="17" t="n"/>
+      <c r="E23" s="16" t="n"/>
+      <c r="F23" s="16" t="n"/>
+      <c r="G23" s="18" t="n"/>
+      <c r="H23" s="17" t="n"/>
+      <c r="I23" s="17" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="16" t="n"/>
+      <c r="B24" s="17" t="n"/>
+      <c r="C24" s="18" t="n"/>
+      <c r="D24" s="17" t="n"/>
+      <c r="E24" s="16" t="n"/>
+      <c r="F24" s="16" t="n"/>
+      <c r="G24" s="18" t="n"/>
+      <c r="H24" s="17" t="n"/>
+      <c r="I24" s="17" t="n"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="16" t="n"/>
+      <c r="B25" s="17" t="n"/>
+      <c r="C25" s="18" t="n"/>
+      <c r="D25" s="17" t="n"/>
+      <c r="E25" s="16" t="n"/>
+      <c r="F25" s="16" t="n"/>
+      <c r="G25" s="18" t="n"/>
+      <c r="H25" s="17" t="n"/>
+      <c r="I25" s="17" t="n"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="16" t="n"/>
+      <c r="B26" s="17" t="n"/>
+      <c r="C26" s="18" t="n"/>
+      <c r="D26" s="17" t="n"/>
+      <c r="E26" s="16" t="n"/>
+      <c r="F26" s="16" t="n"/>
+      <c r="G26" s="18" t="n"/>
+      <c r="H26" s="17" t="n"/>
+      <c r="I26" s="17" t="n"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="16" t="n"/>
+      <c r="B27" s="17" t="n"/>
+      <c r="C27" s="18" t="n"/>
+      <c r="D27" s="17" t="n"/>
+      <c r="E27" s="16" t="n"/>
+      <c r="F27" s="16" t="n"/>
+      <c r="G27" s="18" t="n"/>
+      <c r="H27" s="17" t="n"/>
+      <c r="I27" s="17" t="n"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="16" t="n"/>
+      <c r="B28" s="17" t="n"/>
+      <c r="C28" s="18" t="n"/>
+      <c r="D28" s="17" t="n"/>
+      <c r="E28" s="16" t="n"/>
+      <c r="F28" s="16" t="n"/>
+      <c r="G28" s="18" t="n"/>
+      <c r="H28" s="17" t="n"/>
+      <c r="I28" s="17" t="n"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="16" t="n"/>
+      <c r="B29" s="17" t="n"/>
+      <c r="C29" s="18" t="n"/>
+      <c r="D29" s="17" t="n"/>
+      <c r="E29" s="16" t="n"/>
+      <c r="F29" s="16" t="n"/>
+      <c r="G29" s="18" t="n"/>
+      <c r="H29" s="17" t="n"/>
+      <c r="I29" s="17" t="n"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="16" t="n"/>
+      <c r="B30" s="17" t="n"/>
+      <c r="C30" s="18" t="n"/>
+      <c r="D30" s="17" t="n"/>
+      <c r="E30" s="16" t="n"/>
+      <c r="F30" s="16" t="n"/>
+      <c r="G30" s="18" t="n"/>
+      <c r="H30" s="17" t="n"/>
+      <c r="I30" s="17" t="n"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="16" t="n"/>
+      <c r="B31" s="17" t="n"/>
+      <c r="C31" s="18" t="n"/>
+      <c r="D31" s="17" t="n"/>
+      <c r="E31" s="16" t="n"/>
+      <c r="F31" s="16" t="n"/>
+      <c r="G31" s="18" t="n"/>
+      <c r="H31" s="17" t="n"/>
+      <c r="I31" s="17" t="n"/>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="16" t="n"/>
+      <c r="B32" s="17" t="n"/>
+      <c r="C32" s="18" t="n"/>
+      <c r="D32" s="17" t="n"/>
+      <c r="E32" s="16" t="n"/>
+      <c r="F32" s="16" t="n"/>
+      <c r="G32" s="18" t="n"/>
+      <c r="H32" s="17" t="n"/>
+      <c r="I32" s="17" t="n"/>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="16" t="n"/>
+      <c r="B33" s="17" t="n"/>
+      <c r="C33" s="18" t="n"/>
+      <c r="D33" s="17" t="n"/>
+      <c r="E33" s="16" t="n"/>
+      <c r="F33" s="16" t="n"/>
+      <c r="G33" s="18" t="n"/>
+      <c r="H33" s="17" t="n"/>
+      <c r="I33" s="17" t="n"/>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="16" t="n"/>
+      <c r="B34" s="17" t="n"/>
+      <c r="C34" s="18" t="n"/>
+      <c r="D34" s="17" t="n"/>
+      <c r="E34" s="16" t="n"/>
+      <c r="F34" s="16" t="n"/>
+      <c r="G34" s="18" t="n"/>
+      <c r="H34" s="17" t="n"/>
+      <c r="I34" s="17" t="n"/>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="16" t="n"/>
+      <c r="B35" s="17" t="n"/>
+      <c r="C35" s="18" t="n"/>
+      <c r="D35" s="17" t="n"/>
+      <c r="E35" s="16" t="n"/>
+      <c r="F35" s="16" t="n"/>
+      <c r="G35" s="18" t="n"/>
+      <c r="H35" s="17" t="n"/>
+      <c r="I35" s="17" t="n"/>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="16" t="n"/>
+      <c r="B36" s="17" t="n"/>
+      <c r="C36" s="18" t="n"/>
+      <c r="D36" s="17" t="n"/>
+      <c r="E36" s="16" t="n"/>
+      <c r="F36" s="16" t="n"/>
+      <c r="G36" s="18" t="n"/>
+      <c r="H36" s="17" t="n"/>
+      <c r="I36" s="17" t="n"/>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="16" t="n"/>
+      <c r="B37" s="17" t="n"/>
+      <c r="C37" s="18" t="n"/>
+      <c r="D37" s="17" t="n"/>
+      <c r="E37" s="16" t="n"/>
+      <c r="F37" s="16" t="n"/>
+      <c r="G37" s="18" t="n"/>
+      <c r="H37" s="17" t="n"/>
+      <c r="I37" s="17" t="n"/>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="16" t="n"/>
+      <c r="B38" s="17" t="n"/>
+      <c r="C38" s="18" t="n"/>
+      <c r="D38" s="17" t="n"/>
+      <c r="E38" s="16" t="n"/>
+      <c r="F38" s="16" t="n"/>
+      <c r="G38" s="18" t="n"/>
+      <c r="H38" s="17" t="n"/>
+      <c r="I38" s="17" t="n"/>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="16" t="n"/>
+      <c r="B39" s="17" t="n"/>
+      <c r="C39" s="18" t="n"/>
+      <c r="D39" s="17" t="n"/>
+      <c r="E39" s="16" t="n"/>
+      <c r="F39" s="16" t="n"/>
+      <c r="G39" s="18" t="n"/>
+      <c r="H39" s="17" t="n"/>
+      <c r="I39" s="17" t="n"/>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="16" t="n"/>
+      <c r="B40" s="17" t="n"/>
+      <c r="C40" s="18" t="n"/>
+      <c r="D40" s="17" t="n"/>
+      <c r="E40" s="16" t="n"/>
+      <c r="F40" s="16" t="n"/>
+      <c r="G40" s="18" t="n"/>
+      <c r="H40" s="17" t="n"/>
+      <c r="I40" s="17" t="n"/>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="16" t="n"/>
+      <c r="B41" s="17" t="n"/>
+      <c r="C41" s="18" t="n"/>
+      <c r="D41" s="17" t="n"/>
+      <c r="E41" s="16" t="n"/>
+      <c r="F41" s="16" t="n"/>
+      <c r="G41" s="18" t="n"/>
+      <c r="H41" s="17" t="n"/>
+      <c r="I41" s="17" t="n"/>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="16" t="n"/>
+      <c r="B42" s="17" t="n"/>
+      <c r="C42" s="18" t="n"/>
+      <c r="D42" s="17" t="n"/>
+      <c r="E42" s="16" t="n"/>
+      <c r="F42" s="16" t="n"/>
+      <c r="G42" s="18" t="n"/>
+      <c r="H42" s="17" t="n"/>
+      <c r="I42" s="17" t="n"/>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="16" t="n"/>
+      <c r="B43" s="17" t="n"/>
+      <c r="C43" s="18" t="n"/>
+      <c r="D43" s="17" t="n"/>
+      <c r="E43" s="16" t="n"/>
+      <c r="F43" s="16" t="n"/>
+      <c r="G43" s="18" t="n"/>
+      <c r="H43" s="17" t="n"/>
+      <c r="I43" s="17" t="n"/>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="16" t="n"/>
+      <c r="B44" s="17" t="n"/>
+      <c r="C44" s="18" t="n"/>
+      <c r="D44" s="17" t="n"/>
+      <c r="E44" s="16" t="n"/>
+      <c r="F44" s="16" t="n"/>
+      <c r="G44" s="18" t="n"/>
+      <c r="H44" s="17" t="n"/>
+      <c r="I44" s="17" t="n"/>
+    </row>
+    <row r="45"/>
+    <row r="46" ht="24.5" customHeight="1">
+      <c r="A46" s="19" t="inlineStr">
+        <is>
+          <t>En caso de alerta alimentaria: localizar el lote afectado en esta hoja, seguirlo en «Salida y uso interno» para saber a qué elaboraciones y servicios fue, retirar el producto y notificar de inmediato a la autoridad sanitaria de tu comunidad autónoma (art. 19 del Reg. (CE) 178/2002) y al proveedor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="24.5" customHeight="1">
+      <c r="A47" s="19" t="inlineStr">
+        <is>
+          <t>La información de trazabilidad debe poder entregarse de forma inmediata a requerimiento de la autoridad competente (Reg. (CE) 178/2002, art. 18). El reglamento no fija un plazo de «4 horas»: ese es un requisito de estándares privados tipo IFS/BRC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="12.2" customHeight="1">
+      <c r="A48" s="19" t="inlineStr">
+        <is>
+          <t>Conservar al menos 2 años (trazabilidad y proveedores: 5); el Reg. (CE) 178/2002 exige trazabilidad pero no fija plazo — consulta la guía de prácticas correctas de higiene de tu comunidad autónoma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="12.2" customHeight="1">
+      <c r="A49" s="19" t="inlineStr">
         <is>
           <t>— Pack de Plantillas APPCC · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
+    <row r="50"/>
+    <row r="51"/>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="5">
+    <mergeCell ref="A46:I46"/>
+    <mergeCell ref="A48:I48"/>
+    <mergeCell ref="A47:I47"/>
+    <mergeCell ref="A49:I49"/>
     <mergeCell ref="A1:I1"/>
   </mergeCells>
-  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageMargins left="0.55" right="0.55" top="0.55" bottom="0.55" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>Registro de Trazabilidad — Salida y uso interno (trazabilidad hacia adelante)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Mes: _______________    Anota aquí en qué elaboración y a qué servicio fue cada lote de la hoja «Trazabilidad».</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>Fecha de salida</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Lote de origen (→ hoja Trazabilidad)</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Elaboración / plato</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>Destino / servicio</t>
+        </is>
+      </c>
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="G4" s="15" t="inlineStr">
+        <is>
+          <t>Observaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>06/09/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>L-2026-0912</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>Merluza a la bilbaína (12 raciones)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>4,2 kg</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>Servicio de mediodía — sala</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>A.R.</t>
+        </is>
+      </c>
+      <c r="G5" s="21" t="inlineStr">
+        <is>
+          <t>(ejemplo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>L-2026-0913</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>Estofado de ternera (tanda de 30 raciones)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>9 kg</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>Catering empresa Nordel</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>M.S.</t>
+        </is>
+      </c>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>(ejemplo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="20" t="n"/>
+      <c r="B7" s="21" t="n"/>
+      <c r="C7" s="21" t="n"/>
+      <c r="D7" s="20" t="n"/>
+      <c r="E7" s="21" t="n"/>
+      <c r="F7" s="20" t="n"/>
+      <c r="G7" s="21" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="20" t="n"/>
+      <c r="B8" s="21" t="n"/>
+      <c r="C8" s="21" t="n"/>
+      <c r="D8" s="20" t="n"/>
+      <c r="E8" s="21" t="n"/>
+      <c r="F8" s="20" t="n"/>
+      <c r="G8" s="21" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="20" t="n"/>
+      <c r="B9" s="21" t="n"/>
+      <c r="C9" s="21" t="n"/>
+      <c r="D9" s="20" t="n"/>
+      <c r="E9" s="21" t="n"/>
+      <c r="F9" s="20" t="n"/>
+      <c r="G9" s="21" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="20" t="n"/>
+      <c r="B10" s="21" t="n"/>
+      <c r="C10" s="21" t="n"/>
+      <c r="D10" s="20" t="n"/>
+      <c r="E10" s="21" t="n"/>
+      <c r="F10" s="20" t="n"/>
+      <c r="G10" s="21" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="20" t="n"/>
+      <c r="B11" s="21" t="n"/>
+      <c r="C11" s="21" t="n"/>
+      <c r="D11" s="20" t="n"/>
+      <c r="E11" s="21" t="n"/>
+      <c r="F11" s="20" t="n"/>
+      <c r="G11" s="21" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="20" t="n"/>
+      <c r="B12" s="21" t="n"/>
+      <c r="C12" s="21" t="n"/>
+      <c r="D12" s="20" t="n"/>
+      <c r="E12" s="21" t="n"/>
+      <c r="F12" s="20" t="n"/>
+      <c r="G12" s="21" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="20" t="n"/>
+      <c r="B13" s="21" t="n"/>
+      <c r="C13" s="21" t="n"/>
+      <c r="D13" s="20" t="n"/>
+      <c r="E13" s="21" t="n"/>
+      <c r="F13" s="20" t="n"/>
+      <c r="G13" s="21" t="n"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="20" t="n"/>
+      <c r="B14" s="21" t="n"/>
+      <c r="C14" s="21" t="n"/>
+      <c r="D14" s="20" t="n"/>
+      <c r="E14" s="21" t="n"/>
+      <c r="F14" s="20" t="n"/>
+      <c r="G14" s="21" t="n"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="20" t="n"/>
+      <c r="B15" s="21" t="n"/>
+      <c r="C15" s="21" t="n"/>
+      <c r="D15" s="20" t="n"/>
+      <c r="E15" s="21" t="n"/>
+      <c r="F15" s="20" t="n"/>
+      <c r="G15" s="21" t="n"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="20" t="n"/>
+      <c r="B16" s="21" t="n"/>
+      <c r="C16" s="21" t="n"/>
+      <c r="D16" s="20" t="n"/>
+      <c r="E16" s="21" t="n"/>
+      <c r="F16" s="20" t="n"/>
+      <c r="G16" s="21" t="n"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="20" t="n"/>
+      <c r="B17" s="21" t="n"/>
+      <c r="C17" s="21" t="n"/>
+      <c r="D17" s="20" t="n"/>
+      <c r="E17" s="21" t="n"/>
+      <c r="F17" s="20" t="n"/>
+      <c r="G17" s="21" t="n"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="20" t="n"/>
+      <c r="B18" s="21" t="n"/>
+      <c r="C18" s="21" t="n"/>
+      <c r="D18" s="20" t="n"/>
+      <c r="E18" s="21" t="n"/>
+      <c r="F18" s="20" t="n"/>
+      <c r="G18" s="21" t="n"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="20" t="n"/>
+      <c r="B19" s="21" t="n"/>
+      <c r="C19" s="21" t="n"/>
+      <c r="D19" s="20" t="n"/>
+      <c r="E19" s="21" t="n"/>
+      <c r="F19" s="20" t="n"/>
+      <c r="G19" s="21" t="n"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="20" t="n"/>
+      <c r="B20" s="21" t="n"/>
+      <c r="C20" s="21" t="n"/>
+      <c r="D20" s="20" t="n"/>
+      <c r="E20" s="21" t="n"/>
+      <c r="F20" s="20" t="n"/>
+      <c r="G20" s="21" t="n"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="20" t="n"/>
+      <c r="B21" s="21" t="n"/>
+      <c r="C21" s="21" t="n"/>
+      <c r="D21" s="20" t="n"/>
+      <c r="E21" s="21" t="n"/>
+      <c r="F21" s="20" t="n"/>
+      <c r="G21" s="21" t="n"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="20" t="n"/>
+      <c r="B22" s="21" t="n"/>
+      <c r="C22" s="21" t="n"/>
+      <c r="D22" s="20" t="n"/>
+      <c r="E22" s="21" t="n"/>
+      <c r="F22" s="20" t="n"/>
+      <c r="G22" s="21" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="20" t="n"/>
+      <c r="B23" s="21" t="n"/>
+      <c r="C23" s="21" t="n"/>
+      <c r="D23" s="20" t="n"/>
+      <c r="E23" s="21" t="n"/>
+      <c r="F23" s="20" t="n"/>
+      <c r="G23" s="21" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="20" t="n"/>
+      <c r="B24" s="21" t="n"/>
+      <c r="C24" s="21" t="n"/>
+      <c r="D24" s="20" t="n"/>
+      <c r="E24" s="21" t="n"/>
+      <c r="F24" s="20" t="n"/>
+      <c r="G24" s="21" t="n"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="20" t="n"/>
+      <c r="B25" s="21" t="n"/>
+      <c r="C25" s="21" t="n"/>
+      <c r="D25" s="20" t="n"/>
+      <c r="E25" s="21" t="n"/>
+      <c r="F25" s="20" t="n"/>
+      <c r="G25" s="21" t="n"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="20" t="n"/>
+      <c r="B26" s="21" t="n"/>
+      <c r="C26" s="21" t="n"/>
+      <c r="D26" s="20" t="n"/>
+      <c r="E26" s="21" t="n"/>
+      <c r="F26" s="20" t="n"/>
+      <c r="G26" s="21" t="n"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="20" t="n"/>
+      <c r="B27" s="21" t="n"/>
+      <c r="C27" s="21" t="n"/>
+      <c r="D27" s="20" t="n"/>
+      <c r="E27" s="21" t="n"/>
+      <c r="F27" s="20" t="n"/>
+      <c r="G27" s="21" t="n"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="20" t="n"/>
+      <c r="B28" s="21" t="n"/>
+      <c r="C28" s="21" t="n"/>
+      <c r="D28" s="20" t="n"/>
+      <c r="E28" s="21" t="n"/>
+      <c r="F28" s="20" t="n"/>
+      <c r="G28" s="21" t="n"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="20" t="n"/>
+      <c r="B29" s="21" t="n"/>
+      <c r="C29" s="21" t="n"/>
+      <c r="D29" s="20" t="n"/>
+      <c r="E29" s="21" t="n"/>
+      <c r="F29" s="20" t="n"/>
+      <c r="G29" s="21" t="n"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="20" t="n"/>
+      <c r="B30" s="21" t="n"/>
+      <c r="C30" s="21" t="n"/>
+      <c r="D30" s="20" t="n"/>
+      <c r="E30" s="21" t="n"/>
+      <c r="F30" s="20" t="n"/>
+      <c r="G30" s="21" t="n"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="20" t="n"/>
+      <c r="B31" s="21" t="n"/>
+      <c r="C31" s="21" t="n"/>
+      <c r="D31" s="20" t="n"/>
+      <c r="E31" s="21" t="n"/>
+      <c r="F31" s="20" t="n"/>
+      <c r="G31" s="21" t="n"/>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="20" t="n"/>
+      <c r="B32" s="21" t="n"/>
+      <c r="C32" s="21" t="n"/>
+      <c r="D32" s="20" t="n"/>
+      <c r="E32" s="21" t="n"/>
+      <c r="F32" s="20" t="n"/>
+      <c r="G32" s="21" t="n"/>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="20" t="n"/>
+      <c r="B33" s="21" t="n"/>
+      <c r="C33" s="21" t="n"/>
+      <c r="D33" s="20" t="n"/>
+      <c r="E33" s="21" t="n"/>
+      <c r="F33" s="20" t="n"/>
+      <c r="G33" s="21" t="n"/>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="20" t="n"/>
+      <c r="B34" s="21" t="n"/>
+      <c r="C34" s="21" t="n"/>
+      <c r="D34" s="20" t="n"/>
+      <c r="E34" s="21" t="n"/>
+      <c r="F34" s="20" t="n"/>
+      <c r="G34" s="21" t="n"/>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="20" t="n"/>
+      <c r="B35" s="21" t="n"/>
+      <c r="C35" s="21" t="n"/>
+      <c r="D35" s="20" t="n"/>
+      <c r="E35" s="21" t="n"/>
+      <c r="F35" s="20" t="n"/>
+      <c r="G35" s="21" t="n"/>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="20" t="n"/>
+      <c r="B36" s="21" t="n"/>
+      <c r="C36" s="21" t="n"/>
+      <c r="D36" s="20" t="n"/>
+      <c r="E36" s="21" t="n"/>
+      <c r="F36" s="20" t="n"/>
+      <c r="G36" s="21" t="n"/>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="20" t="n"/>
+      <c r="B37" s="21" t="n"/>
+      <c r="C37" s="21" t="n"/>
+      <c r="D37" s="20" t="n"/>
+      <c r="E37" s="21" t="n"/>
+      <c r="F37" s="20" t="n"/>
+      <c r="G37" s="21" t="n"/>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="20" t="n"/>
+      <c r="B38" s="21" t="n"/>
+      <c r="C38" s="21" t="n"/>
+      <c r="D38" s="20" t="n"/>
+      <c r="E38" s="21" t="n"/>
+      <c r="F38" s="20" t="n"/>
+      <c r="G38" s="21" t="n"/>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="20" t="n"/>
+      <c r="B39" s="21" t="n"/>
+      <c r="C39" s="21" t="n"/>
+      <c r="D39" s="20" t="n"/>
+      <c r="E39" s="21" t="n"/>
+      <c r="F39" s="20" t="n"/>
+      <c r="G39" s="21" t="n"/>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="20" t="n"/>
+      <c r="B40" s="21" t="n"/>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="20" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="20" t="n"/>
+      <c r="G40" s="21" t="n"/>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="20" t="n"/>
+      <c r="B41" s="21" t="n"/>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="20" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="20" t="n"/>
+      <c r="G41" s="21" t="n"/>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="20" t="n"/>
+      <c r="B42" s="21" t="n"/>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="20" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="20" t="n"/>
+      <c r="G42" s="21" t="n"/>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="20" t="n"/>
+      <c r="B43" s="21" t="n"/>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="20" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="20" t="n"/>
+      <c r="G43" s="21" t="n"/>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="20" t="n"/>
+      <c r="B44" s="21" t="n"/>
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="20" t="n"/>
+      <c r="E44" s="21" t="n"/>
+      <c r="F44" s="20" t="n"/>
+      <c r="G44" s="21" t="n"/>
+    </row>
+    <row r="45"/>
+    <row r="46" ht="12.2" customHeight="1">
+      <c r="A46" s="19" t="inlineStr">
+        <is>
+          <t>Una salida por línea. Si un lote se reparte entre varias elaboraciones o servicios, usa una línea por cada uno: es lo que permite acotar la retirada a lo que de verdad salió.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="24.5" customHeight="1">
+      <c r="A47" s="19" t="inlineStr">
+        <is>
+          <t>Conservar al menos 2 años (trazabilidad y proveedores: 5); el Reg. (CE) 178/2002 exige trazabilidad pero no fija plazo — consulta la guía de prácticas correctas de higiene de tu comunidad autónoma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="12.2" customHeight="1">
+      <c r="A48" s="19" t="inlineStr">
+        <is>
+          <t>— Pack de Plantillas APPCC · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A48:G48"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A47:G47"/>
+    <mergeCell ref="A46:G46"/>
+  </mergeCells>
+  <pageMargins left="0.55" right="0.55" top="0.55" bottom="0.55" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>

--- a/astro-site/public/dl/pack-appcc/06-registro-trazabilidad.xlsx
+++ b/astro-site/public/dl/pack-appcc/06-registro-trazabilidad.xlsx
@@ -1387,8 +1387,8 @@
   <mergeCells count="5">
     <mergeCell ref="A46:I46"/>
     <mergeCell ref="A48:I48"/>
+    <mergeCell ref="A49:I49"/>
     <mergeCell ref="A47:I47"/>
-    <mergeCell ref="A49:I49"/>
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.55" right="0.55" top="0.55" bottom="0.55" header="0.3" footer="0.3"/>
